--- a/wishi/wishi_instagram_post_catalog.xlsx
+++ b/wishi/wishi_instagram_post_catalog.xlsx
@@ -7,13 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Posts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pillar Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 15" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In The Bag Playbook" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="in the bag Remakes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Posts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pillar Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 15" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In The Bag Playbook" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Posts'!$A$1:$L$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'in the bag Remakes'!$A$1:$L$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Posts'!$A$1:$L$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,8 +442,6022 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L103"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>in the bag Caption (ready to post)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Visual Brief</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Comment Keyword</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Featured Stylist</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>When to Post</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Content Pillar</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Wishi Original Hook</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Wishi Engagement</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Wishi Link</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Comment NIKKI and we'll send you the full outfit. ✨
+Polka dots are back, and Nikki doesn't do them safe. Sharp tailoring, one statement shoe, a red lip. Polished on the surface, real heat underneath.
+Want a look that makes people notice you before you say a word? Answer Nikki's six questions. The call is free.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Nikki in (or styling) one bold trend piece, full-length, flash-lit.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>NIKKI</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Nikki</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Any week, trend moment</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Stylist Spotlight</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Comment ADRIANA and we'll send you the full outfit details.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZGK4OlIATJ/</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>The clothes come with a stylist.
+Six questions. Four rules that only fit you. One 15-minute call.
+Free. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Close crop: hand adjusting a hem or cuff. Text: 'The clothes come with a stylist.'</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>The difference is in the styling.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZIdXSaIHB7/</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Less time deciding what to wear.
+More time for literally anything else.
+My four rules, from my in the bag stylist:
+1. [rule]
+2. [rule]
+3. [rule]
+4. [rule]
+I got them on a 15-minute call. For free.
+Comment RULES and we'll send you the six questions.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Client POV: getting dressed for work in 10 seconds, text overlay of her four rules (with permission).</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Client POV / Real Client</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Less time deciding what to wear. More time focusing on what matters.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZLQcyVxe2u/</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>A few things living rent-free in Hanna's head...
+The pieces she's wearing on repeat.
+The ones she packs first.
+The ones she tells client after client to look for.
+Not trends. Not impulse buys. Just shapes that keep working.
+Want to know which shapes work on you? That's what her four rules are for. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Flat lay of Hanna's on-repeat pieces on a bed or rail.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Hanna</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Stylist Spotlight</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>A few things currently living rent-free in Adriana's mind...</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZNjkVgk7-_/</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>The right bag changes everything.
+It makes the white tee feel finished.
+The airport outfit look on purpose.
+The jeans feel like a look.
+You probably don't need more things. You need the few that work harder.
+Your stylist knows which ones. Six questions, link in bio.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>One hero bag styled three ways in a 3-up grid.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Hero Piece</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>The right summer bag changes everything.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZQPMnvk5Sq/</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Your bag says a lot about you. (Probably more than you'd like.)
+The tote that goes everywhere.
+The clutch that only comes out after dark.
+The crossbody for the 'I have errands and a lunch' days.
+Swipe through and tell us: which one are you? 👇</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Bag guide: 5 bag shapes, one per slide, each with a personality line. Last slide: 'Which one are you?'</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Guide / Quiz</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Your summer bag says a lot about your style.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZSy6EJD6hA/</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>♊️ Gemini season. One sign, at least two outfits.
+Polished at 9. Playful at 9pm. Both are you.
+Your stylist can build looks for every side. Start with six questions. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Split-screen outfit: polished left half, playful right half.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Gemini season (May 21–Jun 20)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Astrology Season</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Gemini Season is all about versatility.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZVh7iMk4Fd/</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Most guys don't need a bigger wardrobe. They need a smarter one.
+The linen shirt.
+The good polo.
+The sneaker that works with trousers.
+A handful of pieces that make getting dressed automatic.
+Swipe for the 10 pieces Krish recommends again and again.
+Or skip the guesswork: answer the six questions and get rules written for you.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>10 essentials, one per slide, clean background.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Krish</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Father's Day lead-up / any week for menswear</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Menswear / Father's Day</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Most men don't need a bigger wardrobe. They need a smarter one.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZYLUNxE63o/</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Saturday golf.
+The kid's soccer game.
+A backyard grill that somehow runs til 10.
+The moments he remembers aren't about what he wore. But feeling put-together for them still matters.
+This Father's Day, send him the six questions. A stylist calls him for 15 minutes. It's free, so you can still buy the grill tools.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Dad on the sidelines / golf course, easy polished look.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2 weeks before Father's Day</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Menswear / Father's Day</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>The World Cup. Saturday golf. A pickup basketball game.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZalzDIE-Ba/</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>This is what happens when a guy gets fifteen minutes with Carlos.
+Same closet.
+Outfits that finally make sense.
+No shopping spree required.
+Comment DAD and we'll send you the link to set one up for him. It's free.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Before/after: same guy, same closet, restyled by Carlos.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>DAD</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10 days before Father's Day</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Menswear / Father's Day</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>This is what happens when a guy gets styled by Wishi.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZc2NhAR7hG/</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>If cool is the goal, Jo's got it.
+Playing with proportions. Pairing things you'd never think to put together. The one detail that makes it look effortless (it wasn't).
+Want to stop texting the group chat 'what do I wear'? Answer Jo's six questions. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Jo's cool-girl edit: unexpected pairings, one statement detail.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Jo</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Stylist Spotlight</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>If cool is the goal, Connor's got the edit.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZfhpzyj0cp/</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>For the dad who never asks for anything.
+Give him 15 minutes with a stylist. Free.
+Comment DAD and we'll send you the link.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Simple text card over a dad's closet.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>DAD</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1 week before Father's Day</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Menswear / Father's Day</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>For the dad who never asks for anything.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZhnkXmE9JQ/</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Every event turns into a shopping project.
+The vacation.
+The family photo.
+The wedding weekend.
+Scroll. Order. Return. Repeat.
+Or: four rules that tell you what actually works on you, so you only buy what fits them.
+Comment LOOKS and we'll send you the looks.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Event cards: vacation, family photo, wedding weekend, each with one outfit.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>LOOKS</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Start of summer / any big-event season</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Occasion / Event</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Summer has a way of turning every event into a shopping project.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZk0_oNGRTy/</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Plans booked?
+Now let's talk about what you're wearing. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Calendar with plans circled, outfit hanging next to it.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Start of a season</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal / Monthly</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Summer plans booked? Now let's talk about what you're wearing.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZneV1Ok03E/</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>[Month] said warm. The weather said 'maybe.' 😉
+Three layered looks from Sarah Gallagher, built from pieces you probably already own.
+Comment [MONTH] and we'll send you every piece. 🤍</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3 layered looks, one per slide; slide 4 'Comment [MONTH]'.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>[MONTH]</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Gallagher</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Any month (swap month name)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Shoppable Looks (Comment-to-Shop)</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>June said warm. The weather said "maybe."</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZqQX1TGXc9/</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Summer is close enough to taste. ☀️
+Beach days. Late dinners. Weekend trips. The calendar's filling up, but is your closet ready?
+Six questions. Four rules. A stylist calls. Free. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Bright seasonal flat lay.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2 weeks before a season</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal / Monthly</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Summer is so close, we can practically taste it.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZsBot1jMun/</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Summer starts this weekend. ☀️
+The beach days, the weddings, the long weekends are already on the calendar.
+Now: what you're wearing.
+Your stylist writes four rules for your colouring, your proportions, and your plans, then calls to walk you through them.
+No scrolling. No guessing. No card.
+Comment SUMMER to get started.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Quick cuts of season moments + text overlays.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>SUMMER</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Week a new season starts</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal / Monthly</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Summer starts this weekend.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZu4uBIRiXq/</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Summer dressing, simplified.
+Think: one great swimsuit, woven textures, separates that mix, and accessories doing the heavy lifting.
+If your closet needs a reset, Elise is your person. Answer her six questions through the link in bio.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Elise's seasonal edit: swim, woven textures, easy separates.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Start of a season</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Stylist Spotlight</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Summer dressing, simplified.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZxc8wMk0-S/</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Still need a Father's Day gift?
+Skip the gadget. The golf balls. The gift card he'll lose.
+Send him six questions. A stylist calls him for 15 minutes and builds him a whole look from what he already owns.
+Free. Takes two minutes to set up. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Fast text-on-screen reel crossing out gift clichés.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Day before Father's Day</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Menswear / Father's Day</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Still looking for the perfect Father's Day gift?</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ0VS9pRvvD/</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>The first day of summer calls for linen.
+The fabric we tell clients to buy year after year. It travels, it breathes, it gets better the more you wear it.
+This is The Linen Edit: the shapes and textures we're loving right now.
+☀️ Save it for your next shopping trip.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>The Linen Edit: silhouettes and texture close-ups.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>First day of summer</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Category Edit</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>The first day of Summer calls for linen.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ21-vbkQJ4/</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Your vacation should feel easy. So should packing for it.
+Tell your stylist where you're going. They'll tell you what actually works on you, and what can stay home.
+Comment TRIP to get started. ☀️</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Open suitcase with a tidy capsule inside.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>TRIP</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Before summer travel</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Travel / Packing</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Summer should feel easy. Your vacation wardrobe should too.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5WLhBky5U/</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Packing isn't about bringing more.
+It's about bringing what works.
+One carry-on. Seven pieces. Ten outfits.
+Need help with your next trip? Comment TRIP and we'll send you the six questions.</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>One carry-on, 7 pieces, 10 outfits.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>TRIP</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Before travel season</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Travel / Packing</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Packing isn't about bringing more.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ74IWMk4vQ/</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Meet Hanna. Stylist. 12 years. (And a real-life 27 Dresses.)
+'I'm not here to dress you like me, or talk you into replacing everything you own.'
+This is my capsule right now, and what I tell every client:
+Keep what works.
+Buy only what's worth it.
+Get more outfits out of what's already hanging there.
+Welcome to my closet.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Hanna's personal capsule + portrait on slide 1.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Hanna</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Any week (founder post)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Founder / Leader Capsule</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Meet Zu. President of WISHI. Stylist.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ-ll5IGVtA/</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Life doesn't come with a dress code.
+Your stylist makes getting dressed the easy part. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Same woman, three settings (work, wedding, weekend).</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Because life doesn't come with a dress code.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaA1t8wkwE6/</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>The internet is chaotic.
+Getting dressed shouldn't be.
+Instead of 20 open tabs, get four rules written for your colouring, your proportions, and your life.
+No more guessing.
+No more impulse buys.
+No more 'it looked different on the model.'
+Comment RULES to get started. It's free.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Text-only reel: chaotic tabs closing one by one.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Any week (hero reel; boost this one)</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>The internet is chaotic. Your shopping experience shouldn't be.</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaDecYLxz8B/</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Imagine opening your closet and already knowing what works.
+Shopping gives you options.
+A stylist gives you rules.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Closet door opening onto an organised rail.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Imagine opening your closet and already knowing what to wear.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaFqtOUGSig/</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>[Holiday] is next week. Are you styled for it?
+The beach day.
+The barbecue.
+The weekend away.
+The dinner reservation.
+We'll help with the outfits. You handle the memories.
+Comment STYLE for the six questions.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Holiday looks: beach, barbecue, dinner.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>STYLE</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1 week before a holiday weekend</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Holiday / Promo</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>4th of July is next week. Are you styled for it?</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaI4Jz0E-sO/</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>The sales are happening.
+Don't shop them blind.
+Know your four rules first: your colours, where your hems should sit, the shapes that always work. Then buy only what fits them.
+The call is free. The rules don't expire. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Shopping bags + a crossed-out 'add to cart'.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>During big sale events</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Holiday / Promo</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>The sales are happening. Don't shop them alone.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaLuoZRE8jY/</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>The best thing you'll get from this sale isn't in your cart.
+It's knowing which pieces are worth it.
+Fifteen minutes with a stylist before you check out. Four rules that only fit you. Free.
+No endless scrolling. No 'I'll return it.' Just the right buys.
+Link in bio.</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Voiceover reel, 'sale ends tonight' energy.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Last day of a sale event</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Holiday / Promo</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>The best purchase you'll make this summer isn't another piece of clothing.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaNyiQ0R0sR/</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>[Month] has plans for you. Your closet should too.
+Trips, weddings, the office, the holiday weekend. Your stylist builds a look around your life, not the latest trend.
+Start the month with six questions. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Month name in big type over a styled outfit.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1st of the month</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal / Monthly</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>July has plans for you. Your wardrobe should, too.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaQgwlNkyav/</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Wedding invitations show up all at once.
+(Hanna would know. Real-life 27 Dresses, remember?)
+Instead of panic-buying another dress, let her show you one that works for three weddings, and dinner after.
+The best guest looks aren't the most expensive. They're the ones you wear again.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>3 wedding-guest looks that re-wear.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Hanna</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Wedding season</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Occasion / Event</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Wedding invitations have a way of showing up all at once.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaTBlSXmc3q/</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Long weekends deserve outfits that keep up.
+Golden hour. Dinner by the water. Brunch that turns into the whole day.
+Know what you're wearing before you pack. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Golden-hour clips, outfit transitions.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Before a long weekend</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Holiday / Promo</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Long weekends deserve a wardrobe that keeps up.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaVfqzbxkc2/</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Happy [holiday]. 🤍
+Here's to long lunches, late nights, and friends who stay longer than planned.
+Have a beautiful weekend.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Warm holiday photo, no product.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>On the holiday</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Holiday / Promo</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Happy Fourth.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaXsRuCks5b/</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>The best outfits aren't picked the night before.
+Before the work trip.
+Before the wedding invite.
+Before the birthday dinner.
+Before you're standing in front of your closet with nothing to wear.
+That's why the six questions ask what's coming up, not just what's in your closet.
+Link in bio.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Calendar flipping, outfits ready for each event.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>The best wardrobes aren't built the night before.</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daa99tzR_xm/</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>The internet has an opinion on everything.
+A new trend.
+A new aesthetic.
+A new 'must-have.'
+Fifty saved outfits later, still nothing to wear.
+The internet tells you what's popular.
+Your stylist tells you what works on you.</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Phone screen full of saved outfits, crossed out.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>The internet has an opinion about everything.</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DadZTr7mSnk/</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Cancer season. 🦀
+The sign that keeps everything. (Including that dress from 2017.)
+Good news: your stylist will show you how to wear what you already love. No purge required.
+Happy birthday, Cancers. Treat yourself to six questions. 🤍</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Zodiac-themed slides, soft blues and silver.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Cancer season (Jun 21–Jul 22)</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Astrology Season</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>After thousands of styling sessions, one sign books with us more than any other: Cancer.</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DagYda8GXKq/</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>The most stylish people don't start from scratch every morning.
+They have rules.
+Colours that work.
+Shapes they trust.
+Shoes they reach for on repeat.
+That's what your four rules are.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Three outfits built from the same five pieces.</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>The most stylish people don't get dressed from scratch every morning.</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daihz1uExTo/</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Every season, thousands of new arrivals.
+The hard part isn't finding something beautiful.
+It's knowing what works on you.
+Your stylist edits through the noise. Six questions to start. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Rapid-fire new-arrival screenshots, then one clean outfit.</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Start of a season</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Every season brings thousands of new arrivals.</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dald8qTRxFz/</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Summer, styled by Jo. ☀️
+Meet Jo: chic, effortless, a little unexpected.
+- Must-own piece: [Jo's answer]
+- Summer shoe: [Jo's answer]
+- Skipping: [Jo's answer]
+- Never buying: [Jo's answer]
+Love her eye? Answer Jo's six questions and she'll call you. ✨</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Jo Q&amp;A: one answer per slide over her photos.</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Jo</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Start of a season</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Stylist Spotlight</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Summer, Styled by Mika.</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Danr7v7ExzC/</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Real client. Real closet. Real confidence.
+She had a trip coming up and nothing that felt right.
+One 15-minute call. Four rules. She packed half as much.
+Your turn. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Client trip outfits montage (with permission).</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Client POV / Real Client</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Real client. Real wardrobe. Real confidence.</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daqhce1xSNG/</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>The Bag Edit: worth buying.
+Every week, our stylists cut the endless new arrivals down to the few we'd actually recommend.
+This week:
+• [piece]
+• [piece]
+• [piece]
+• [piece]
+• [piece]
+Save it. New edit every Sunday.</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>'The Bag Edit' cover + 5 product slides.</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Every Sunday (weekly series)</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Weekly Series: The Edit</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>The WISHI Edit - Worth Buying.</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Das6rnSE7GE/</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Great closets aren't built by accident.
+They're built one smart buy at a time.
+Your best purchase isn't another piece.
+It's knowing which one to choose.</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Text card over a neat rail.</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Great wardrobes aren't built by accident.</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DavgnvPICRP/</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>[Month], layered right.
+Anyone can buy great pieces. Knowing how to put them together changes everything.
+Three looks from Tessa.
+Comment [MONTH] and we'll send you every piece.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>3 layered looks by Tessa.</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>[MONTH]</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Tessa</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Monthly series (swap month)</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Shoppable Looks (Comment-to-Shop)</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>July, Layered Right.</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax-o8vk-Ml/</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Don't copy the outfit.
+Copy the formula.
+That's what your stylist sees.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Inspo photo with the 'formula' annotated.</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Don't copy the outfit. Copy the formula.</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Da0iv31k8HA/</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>The internet gives you thousands of options.
+Your stylist gives you the right ones.
+Less guessing. Better shopping. A closet that finally works together.
+Six questions. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Endless scroll that stops on one look.</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>The internet gives you thousands of options. Your WISHI stylist gives you the right ones.</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Da28B_HxWto/</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Summer, styled by Diane.
+Meet the stylist behind this week's edit.
+Currently telling clients to buy: [answer]
+Current obsession: [answer]
+Favourite summer piece: [answer]
+Love Diane's point of view? Answer her six questions through the link in bio.</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Diane Q&amp;A slides.</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Start of a season</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Stylist Spotlight</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Summer, Styled by Alia.</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Da5s_OcE42P/</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Real woman.
+Real closet.
+Real stylist.
+Styled around her life, not an algorithm.
+Ready for yours? Link in bio.</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Real client getting ready, no models.</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Client POV / Real Client</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Real woman. Real wardrobe. Real stylist.</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Da8aJpax64f/</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Packing well isn't bringing more. It's bringing the right pieces.
+What our stylists always make room for:
+• An evening sandal
+• The going-out top
+• A small evening bag
+• Easy pants
+• A tote that fits the flight
+• One statement earring
+• The dress that does it all
+Save this before your next trip. ✈️🤍</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Packing list, one item per slide.</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Before travel season</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Travel / Packing</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Packing well isn't about bringing more, it's about bringing the right pieces.</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Da-80d1k7Jb/</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Stop wondering what to buy next.
+Your stylist already knows.
+Six questions. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Text card.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Stop wondering what to buy next. Your stylist already knows.</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbBccDbIJ9q/</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Every call starts with a different answer.
+'I need one dress that does everything.'
+'I'm traveling for ten days and refuse to check a bag.'
+'My closet is full and I still have nothing to wear.'
+Different answers. Same goal: make getting dressed easier.
+What would yours be? Link in bio.</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Real quiz answers / client quotes, one per slide (anonymised).</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Client Requests</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Every styling session starts with a different question.</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbD8rDeGX3k/</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>There's something about a look that feels effortless.
+Nothing overdone. Nothing extra. Just the right pieces, worn like you mean it.</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Pure mood shot, no text.</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Mood / Inspiration</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>There's something about a look that feels effortless.</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbGk7ypkyKW/</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Summer, styled by Sarah Gallagher.
+Everyone has that one person they check with before buying something.
+The one who notices the better fit.
+The better fabric.
+The piece you'll still wear in five years.
+For a lot of our clients, that's Sarah.
+This week's edit is her approach: timeless pieces, thoughtful styling, nothing wasted.</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Gallagher's edit, portrait first.</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Gallagher</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Stylist Spotlight</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Summer, Styled by @clea.</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbJJvdLID0v/</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>What does an in the bag stylist actually do?
+You answer six questions.
+She writes four rules that only fit you, and seals them.
+She calls. Fifteen minutes. She opens them with you.
+She builds a whole look from your closet while you're on the line.
+There's no written version. That's the point.
+Free. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Explainer: quiz on phone → sealed rules → phone call → outfit on the bed.</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Process Explainer</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>What does a stylist actually do?</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbLxqR-xg-G/</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Great closets aren't built in a weekend.
+They're built over time, with the right pieces, added at the right moment.
+It's not about buying everything.
+It's about buying what's worth it.</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Text card over closet.</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>The best wardrobes aren't built in a weekend.</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbNw8tmEyt-/</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>The Bag Edit: worth repeating.
+Some pieces never stop earning their spot.
+The white shirt you grab without thinking.
+The sandals that go everywhere.
+The jewellery you never take off.
+This week: the staples our stylists come back to season after season.
+Save it for your next shopping trip.</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>'The Bag Edit: worth repeating' staples.</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Every Sunday (weekly series)</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Weekly Series: The Edit</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>The WISHI Edit - Worth Repeating</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbQxTMTjiGG/</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>You don't need more clothes.
+You need better rules.
+Four of them. Written for you. Free. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Text card.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>People don't need more clothes. They need better decisions.</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbTekosk3I0/</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Shopping is more fun when you know it'll work.
+No card.
+No box.
+No subscription.
+Just a stylist, six questions, and fifteen minutes on the phone.
+Link in bio.</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Text reel: 'No card. No box. No subscription.'</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Subscription Pitch</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Shopping is more fun when you know you're making the right choice.</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbVz-oAjwHj/</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Getting dressed gets easier the moment you stop doing it alone.
+A good stylist doesn't add more. They add intention.
+What to keep. What to skip. How to make every piece earn its spot.</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Stylist's hands pinning a look on a rail.</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Style gets easier the moment you stop trying to do it all yourself.</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbYmd7Vk4SL/</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Every stylist sees it differently.
+This week, we're stepping inside Nikki's world.
+The pieces she'd buy.
+The trends she'd skip.
+The advice she gives every client.
+Nikki doesn't do safe. Swipe and see. Then answer her six questions through the link in bio.</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>'Inside Nikki's world': buy / skip / advice slides.</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Nikki</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Any week (top format: post on a strong day)</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Stylist Spotlight</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Every stylist sees fashion differently. This week, we're stepping inside Tara's world.</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbbLT64E3It/</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>The best summer outfits aren't complicated.
+They're the ones that feel like you.
+Comfortable. Confident. Ready for wherever the day goes.</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Simple summer outfit, outdoor light.</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Mood / Inspiration</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>The best summer outfits aren't complicated.</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbdiUOmk6kx/</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Hello, [month].
+This month: workdays that end with dinner out, weekend trips, celebrations, and the slow return to routine.
+We'll be sharing what our stylists are wearing, recommending, and reaching for now. Stay close.</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Month kickoff montage.</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>1st of the month</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal / Monthly</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Hello, August.</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbgJYwxjGli/</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Every month brings new trends. We care more about what lasts.
+The [Month] Edit: pieces our stylists think are worth adding now, because they'll work just as well next season.
+Think dark denim. Light knits. A good flat. Chocolate brown accessories.
+Save it. Or let your stylist tell you which ones work on you.</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>'The [Month] Edit' cover + 6 piece slides.</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Start of the month</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Edit</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Every month brings new trends. We're more interested in what lasts.</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dbi_X6HGQBC/</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Four rules. Written for you. Sealed.
+You can see what each one promises. Only your stylist can open them, on the call, with you.
+The colours that make you look rested.
+Where your hems and waists should sit.
+The shapes that always work.
+One whole look, built while you talk.
+Six questions to start. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>The sealed-rules envelope / screen visual.</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Product Feature</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Your next favorite outfit shouldn't take hours to find.</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DblfkSCGXIm/</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Your closet should work as hard as you do.
+Office. Flight. Dinner with friends. Every outfit should feel easy.
+That's the job. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Office-to-dinner outfit.</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Your wardrobe should work as hard as you do.</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DboJgsykx6E/</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>[Month] is all about versatility.
+Light enough for now. Layered enough for what's next.
+Three looks from Lou. Endless ways to wear them.
+See what your stylist would pick: link in bio.</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Three looks by Lou, now → next season.</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Lou</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Season transition</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Three Looks</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>August is all about versatility.</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbsxZ7Rmwp6/</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Your [month] closet should keep up with your calendar.
+Weekend trips.
+Monday meetings.
+Everything in between.
+Six questions. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Calendar + outfit.</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Early in the month</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal / Monthly</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Your August wardrobe should keep up with your calendar.</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dbx0onTmym8/</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>The second half of the month fills up fast.
+Work trips.
+Weddings.
+Long weekends.
+Last-minute dinners.
+The people who always look put together aren't shopping the night before. They planned.
+Fifteen minutes with a stylist. Free.</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>List of upcoming events as text.</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Mid-month</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Calendar-Driven</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>The second half of August fills up fast.</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Db3hs6ik-YX/</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Confidence is the dress code. ♌️
+Golden hour. Big dinners. Making an entrance.
+Nikki's Leo edit: bold, radiant, a little dangerous.
+Wedding, rooftop, or just a Tuesday you want to own.</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Bold, gold, main-character looks.</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Nikki</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Leo season (Jul 23–Aug 22)</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Astrology Season</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Confidence is the dress code.</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Db5pW8amwdL/</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>The best closet refresh doesn't always start with shopping.
+It starts with seeing what you own differently.
+Last season's favourites. A new way to wear them.
+That's literally what the call is: one whole look built from what's already hanging there.</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Old piece restyled with new accessories, before/after.</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Hanna</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Shop Your Closet</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>The best wardrobe updates don't always start with shopping.</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Db8OHBkm9ds/</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>What to wear to [local event: Colts game / Indy 500 / the gala].
+[Item 1].
+[Item 2].
+Comfortable shoes.
+Great sunglasses.
+One unforgettable day.
+Because it's not just a [game/race]. It's one of the best-dressed days of the year.</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>'What to wear to [event]' checklist.</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Day before a big local event</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Occasion / Event</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>What to Wear to the US Open.</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Db-0DahoGar/</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>One event.
+Three ways to wear it.
+In the stands. Dinner after. Making a weekend of it.
+Blake planned every look.
+Plan the outfits. Enjoy the day. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>One event, three looks (day / dinner / weekend).</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Blake</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Week of a big local event</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Occasion / Event</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>One event. Three ways to wear it.</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcBnvdoCUq0/</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>The second half of the month has a habit of filling up.
+Weddings. Long weekends. Dinner reservations.
+Getting dressed shouldn't be another thing on the list. Your stylist makes sure every invite already has an outfit.</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Invitations stacked next to an outfit.</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Mid-month</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Calendar-Driven</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>The second half of August has a habit of filling up fast.</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcJjRD4oHF_/</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>The people who always look put together aren't lucky.
+They have rules.
+Get yours. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Text card.</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>The people who always look put together don't get lucky.</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcOPrckGxNZ/</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>The easiest closet refresh? Accessories.
+Your stylist can show you which ones make what you own feel new again.</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Same outfit, two accessory sets.</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>The easiest summer wardrobe refresh? Accessories.</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcRssacy-nU/</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>The best closets aren't built for one event.
+They're built for real life.
+Morning coffee.
+The commute.
+Lunch.
+Last-minute plans.
+Dinner.
+One outfit that handles all of it. That's what your rules are for.</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Day-in-the-life: coffee, commute, lunch, dinner, one outfit.</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Day-in-the-Life</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>The best wardrobes aren't built for one event. They're built for real life.</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcTnABwEoiQ/</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>You don't need a whole new closet for fall.
+You need the right few pieces.
+Your stylist knows where to start.</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Transitional outfit.</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Late summer / season transition</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal Transition</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>You don't need a whole new wardrobe for fall. You need the right pieces.</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcY-5Mym__9/</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Great closets aren't built in a day.
+They're built one good decision at a time.
+Your rules don't expire. Neither does the advice.</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Text card.</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Subscription Pitch</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>The best wardrobes aren't built in a day.</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcbcQpGm6R-/</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Packing lighter starts long before the suitcase.
+Know your shapes. Know your colours. The rest packs itself.
+Six questions, link in bio.</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Small suitcase, neatly packed.</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Before travel</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Travel / Packing</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Packing lighter starts long before the suitcase.</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcgtRlpoPjl/</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>The best part of the weekend isn't deciding what to wear.
+It's already knowing.</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Weekend outfit transitions.</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Thursday/Friday</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Brand Value Prop</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>The best part of the weekend isn't deciding what to wear. It's already knowing.</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcjKqpSApMi/</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>One weekend.
+One small, smart wardrobe.
+See how Noor turns a few pieces into travel, dinner, and everything in between.
+Want yours built from what you already own? Link in bio.</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>One weekend, 6 pieces, 5 looks by Noor.</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Noor</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Capsule / Outfit Math</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>One weekend. One thoughtfully built wardrobe.</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dclncx_G2S3/</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>The best accessories aren't for one season.
+They're the ones you reach for year after year.
+Your stylist will tell you which ones are worth it.</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Investment accessories still-life.</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>The best accessories aren't just for one season.</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcqyJ5QoPfN/</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>[Month] has a way of arriving all at once.
+Meetings.
+School drop-offs.
+Work trips.
+Client dinners.
+Weekend plans.
+And through it all, you're expected to look like you have it together.
+That's where we come in.
+Four rules for your colouring, your proportions, and your calendar, so you're not shopping the night before.
+You have enough to think about. Let us handle what you wear.
+Six questions. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Rhythmic text list over getting-ready clips. Strong candidate for paid boost.</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>1st of a busy month (Sept/Jan)</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal / Monthly</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>September has a way of arriving all at once.</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcvuAs-gLOt/</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>The best outfits aren't picked five minutes before you leave.
+They're planned around your calendar, your closet, your life.
+That's what your stylist is already thinking about.
+intheb.ag</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Text card over door.</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Calendar-Driven</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>The best outfits aren't chosen five minutes before you walk out the door.</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcyuRSIm5pO/</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Wherever this weekend takes you...
+...arrive feeling like yourself.
+Have a beautiful [holiday] weekend.</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Soft holiday-weekend photo.</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Holiday weekend</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Holiday / Promo</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Wherever this weekend takes you... arrive feeling like yourself.</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dc3qIH1oAqV/</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>One last summer carry.
+The calendar says September. The weather didn't get the memo.
+We're holding onto linen a little longer and slowly bringing back the good stuff:
+Great denim.
+Soft knits.
+The jacket you'll grab every morning.
+🤍 Six questions to start your fall. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Last-of-season bag + first-of-season knit.</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>End of a season</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal Transition</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>One last summer carry.</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dc_fZOgoKJa/</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>[Month], layered right. 🍂
+You have the clothes. You just need the outfits.
+Comment [MONTH] and we'll send you the looks. 🤍</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>3 layered looks; last slide 'Comment [MONTH]'.</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>[MONTH]</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Hanna</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Monthly series (top comment-driver)</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Shoppable Looks (Comment-to-Shop)</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>September, layered right.</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdTxNhioDSU/</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Transition dressing is complicated.
+Too warm for the sweater. Done with summer.
+Start with the pieces that shift everything: the right shoe, the right denim, the right accessories.
+Your stylist knows which ones fit your rules.</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Shoes / denim / accessories slides.</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Season transition</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal Transition</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>September dressing is complicated.</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdcB7jgF2FE/</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>What to wear now, according to Jo.
+In-between weather calls for light layers, playful proportions, and one detail that makes it look effortless: a light trench, a fine knit, a clean skirt, a heeled flat, an easy tote, one big earring.
+Plus Jo's formula for wearing it: relaxed shapes, sharp details, a little contrast.
+Love her eye? Answer Jo's six questions.</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Jo's 6 pieces + 'Jo's formula' slide.</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Jo</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Season transition</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Stylist Spotlight</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>What to wear now, according to Mika.</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddd9hS2jOnd/</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Sunday plans: answering six questions so my stylist knows the vibe.
+Your colouring. Your proportions. Where clothes go wrong on you. What's coming up.
+Two minutes. Then she calls and builds you a look.
+Your taste. Your closet. Your stylist.</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Phone screen: filling in the six questions.</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Product Feature</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Sunday plans: adding to my Wishi collection so my stylist knows the vibe.</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdhEpAWl6DE/</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>The runways have spoken: '90s elegance is back.
+The fun part? Deciding what your version looks like.
+Nikki's take: sharper, sexier, never boring.
+Don't get dressed for the season without your rules.</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Runway trend → real-life versions.</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Nikki</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>After fashion month / trend moment</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Trend Report</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>The runways have spoken: '90s elegance is back.</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdmEvGuEQdY/</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>First day of fall. Your sign to stop scrolling and start getting dressed. 🍂
+Your stylist knows what works on you, what works with what you own, and what you'll actually wear.
+Less searching. Better dressing.</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Leaves / season cues + outfit.</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>First day of a season</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal / Monthly</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>First day of fall. Consider this your sign to stop scrolling.</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdpdYtXj45K/</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Elise knows the difference between simple and just right.
+Rich texture. Easy proportions. The perfect flat. One unexpected detail.
+Less about trends. More about knowing what works.
+Love Elise's eye? Answer her six questions.</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Elise's texture/proportion edit.</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Stylist Spotlight</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Daphne knows the difference between simple and just right.</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddt9KS-jEgO/</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>[Real client review or press quote here.]
+Thank you, [name]. This is exactly why we do it: four rules that fit you, and the confidence to stop guessing.
+Your turn. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Client review screenshot or press clip. Use ONLY real quotes.</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>When you have a real review or press mention</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Press / Social Proof</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>The best fall shopping habit? Knowing what's worth buying.</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddv_CK_oNkg/</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>[This month] was the warm-up. [Next month] has plans.
+School mornings. Meetings. Dinners. Weekends away.
+Your closet should be ready for all of it.
+Six questions. Link in bio.</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Next month's calendar filling up.</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Last week of the month</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal / Monthly</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>September was the warm-up. October has plans.</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdzGKPUCbX6/</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>[This month] was the mood board.
+[Next month] is the outfit.
+Our stylists already know which jackets, knits, and boots are worth it. Now let's find yours.</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Mood board → finished outfit.</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Last day of the month</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal / Monthly</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>September was the mood board. October is the outfit.</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dd7EY6PvNfI/</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>[Month], styled.
+The jackets, knits, and boots worth adding, and how to make them work with what you already own.
+Tell us what's on your calendar. Your stylist handles the outfit.</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Month title card over outfit.</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Start of the month</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal / Monthly</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>October, styled.</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dd-LGaijC8p/</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Why in the bag exists.
+For 12 years I've watched brilliant, busy women stand in front of full closets with nothing to wear.
+You don't need a subscription box or a shopping spree. You need someone who gets you to tell you what works, and why.
+So we made it simple: six questions, four rules, fifteen minutes. Free.
+To everyone who's trusted us with a closet, a big moment, or a new chapter: thank you. 🤍</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Hanna portrait + handwritten note.</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Hanna</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Brand anniversary / launch date</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Brand Story / Anniversary</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Seven years ago, we had a big idea.</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DeCAmqIjLF-/</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Love her style? Let her style you.
+Six in the bag stylists share their take on the season.
+Now make it personal: pick the stylist whose eye you love, answer the six questions, and they'll call you.
+Link in bio.</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Six stylists, one look each.</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Lou, Blake, Tessa, Diane, Noor, Elise</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Season start</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Stylist Roundup</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Love her style? Let her style you.</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DeFGmGhjL9M/</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>[Month], layered right.
+Deep plum tailoring over black. Burgundy lace with relaxed denim. Black leather and gold.
+Three looks from Tessa. Three lessons in contrast.
+Comment [MONTH] and we'll send you the looks.</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>3 contrast looks.</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>[MONTH]</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Tessa</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Monthly series (pin it)</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Shoppable Looks (Comment-to-Shop)</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>October, layered right.</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DeM9CurjGhU/</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Your fall closet needs a little more Nikki.
+She starts with clean lines, then adds the piece that shifts the whole look: cobalt leather, a sharp heel, a print with bite.
+Want her capsule? Comment NIKKI and we'll send it, plus her six questions.</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Nikki's capsule: clean base + one statement piece per look.</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>NIKKI</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Nikki</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Any week</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Stylist Spotlight</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Your fall wardrobe needs a little more Adriana.</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DeR4SKKjAlB/</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Notes: [brackets] = fill in before posting (month, holiday, stylist answers, real reviews). Comment keywords assume a DM auto-reply (e.g. ManyChat) that sends intheb.ag/quiz or the shop list. Only Hanna, Nikki and Jo have public bios on intheb.ag; other stylists' spotlight details are placeholders to confirm with them.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L101"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId100"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -5525,14 +11541,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -6556,14 +12572,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -7676,14 +13692,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
